--- a/TODOS_PLANES_AKADEMIC.xlsx
+++ b/TODOS_PLANES_AKADEMIC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\OneDrive - UNIVERSIDAD AUTONOMA DE ICA\Escritorio\regulazizacion-aka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4D0AA8-E8CC-4821-A809-784E855FD0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0912C3FA-0C51-40EB-AF95-A673A378D90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15513,7 +15513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>2649</v>
       </c>
@@ -15521,19 +15521,19 @@
         <v>402</v>
       </c>
       <c r="C354" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="D354" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="E354" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="I354">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>2649</v>
       </c>
@@ -15541,19 +15541,19 @@
         <v>402</v>
       </c>
       <c r="C355" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="D355" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
       <c r="E355" t="s">
-        <v>405</v>
+        <v>115</v>
       </c>
       <c r="I355">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>2649</v>
       </c>
@@ -15561,19 +15561,19 @@
         <v>402</v>
       </c>
       <c r="C356" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="D356" t="s">
-        <v>624</v>
+        <v>647</v>
       </c>
       <c r="E356" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="I356">
         <v>3</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>2649</v>
       </c>
@@ -15581,19 +15581,19 @@
         <v>402</v>
       </c>
       <c r="C357" t="s">
-        <v>1890</v>
+        <v>1894</v>
       </c>
       <c r="D357" t="s">
-        <v>625</v>
+        <v>653</v>
       </c>
       <c r="E357" t="s">
-        <v>102</v>
+        <v>654</v>
       </c>
       <c r="I357">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>2649</v>
       </c>
@@ -15601,19 +15601,19 @@
         <v>402</v>
       </c>
       <c r="C358" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="D358" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="E358" t="s">
-        <v>409</v>
+        <v>31</v>
       </c>
       <c r="I358">
         <v>3</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>2649</v>
       </c>
@@ -15621,19 +15621,19 @@
         <v>402</v>
       </c>
       <c r="C359" t="s">
-        <v>1890</v>
+        <v>1896</v>
       </c>
       <c r="D359" t="s">
-        <v>627</v>
+        <v>1990</v>
       </c>
       <c r="E359" t="s">
-        <v>21</v>
+        <v>2524</v>
       </c>
       <c r="I359">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>2649</v>
       </c>
@@ -15641,19 +15641,19 @@
         <v>402</v>
       </c>
       <c r="C360" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="D360" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="E360" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I360">
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>2649</v>
       </c>
@@ -15661,19 +15661,19 @@
         <v>402</v>
       </c>
       <c r="C361" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="D361" t="s">
-        <v>629</v>
+        <v>639</v>
       </c>
       <c r="E361" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I361">
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>2649</v>
       </c>
@@ -15681,19 +15681,19 @@
         <v>402</v>
       </c>
       <c r="C362" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="D362" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="E362" t="s">
-        <v>110</v>
+        <v>37</v>
       </c>
       <c r="I362">
         <v>3</v>
       </c>
     </row>
-    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>2649</v>
       </c>
@@ -15701,19 +15701,19 @@
         <v>402</v>
       </c>
       <c r="C363" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D363" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="E363" t="s">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="I363">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>2649</v>
       </c>
@@ -15721,19 +15721,19 @@
         <v>402</v>
       </c>
       <c r="C364" t="s">
-        <v>1891</v>
+        <v>1897</v>
       </c>
       <c r="D364" t="s">
-        <v>632</v>
+        <v>1993</v>
       </c>
       <c r="E364" t="s">
-        <v>31</v>
+        <v>2526</v>
       </c>
       <c r="I364">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>2649</v>
       </c>
@@ -15744,16 +15744,16 @@
         <v>1891</v>
       </c>
       <c r="D365" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E365" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="I365">
         <v>3</v>
       </c>
     </row>
-    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>2649</v>
       </c>
@@ -15761,19 +15761,19 @@
         <v>402</v>
       </c>
       <c r="C366" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="D366" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="E366" t="s">
-        <v>35</v>
+        <v>583</v>
       </c>
       <c r="I366">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>2649</v>
       </c>
@@ -15781,19 +15781,19 @@
         <v>402</v>
       </c>
       <c r="C367" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="D367" t="s">
-        <v>635</v>
+        <v>1986</v>
       </c>
       <c r="E367" t="s">
-        <v>121</v>
+        <v>2520</v>
       </c>
       <c r="I367">
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>2649</v>
       </c>
@@ -15801,19 +15801,19 @@
         <v>402</v>
       </c>
       <c r="C368" t="s">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="D368" t="s">
-        <v>636</v>
+        <v>1987</v>
       </c>
       <c r="E368" t="s">
-        <v>37</v>
+        <v>2521</v>
       </c>
       <c r="I368">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>2649</v>
       </c>
@@ -15821,19 +15821,19 @@
         <v>402</v>
       </c>
       <c r="C369" t="s">
-        <v>1892</v>
+        <v>1896</v>
       </c>
       <c r="D369" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="E369" t="s">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="I369">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>2649</v>
       </c>
@@ -15841,19 +15841,19 @@
         <v>402</v>
       </c>
       <c r="C370" t="s">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="D370" t="s">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="E370" t="s">
-        <v>39</v>
+        <v>600</v>
       </c>
       <c r="I370">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>2649</v>
       </c>
@@ -15861,19 +15861,19 @@
         <v>402</v>
       </c>
       <c r="C371" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="D371" t="s">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="E371" t="s">
-        <v>115</v>
+        <v>596</v>
       </c>
       <c r="I371">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>2649</v>
       </c>
@@ -15881,19 +15881,19 @@
         <v>402</v>
       </c>
       <c r="C372" t="s">
-        <v>1893</v>
+        <v>1897</v>
       </c>
       <c r="D372" t="s">
-        <v>641</v>
+        <v>671</v>
       </c>
       <c r="E372" t="s">
-        <v>49</v>
+        <v>672</v>
       </c>
       <c r="I372">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>2649</v>
       </c>
@@ -15901,19 +15901,19 @@
         <v>402</v>
       </c>
       <c r="C373" t="s">
-        <v>1893</v>
+        <v>1896</v>
       </c>
       <c r="D373" t="s">
-        <v>642</v>
+        <v>669</v>
       </c>
       <c r="E373" t="s">
-        <v>51</v>
+        <v>608</v>
       </c>
       <c r="I373">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>2649</v>
       </c>
@@ -15921,19 +15921,19 @@
         <v>402</v>
       </c>
       <c r="C374" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="D374" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="E374" t="s">
-        <v>53</v>
+        <v>594</v>
       </c>
       <c r="I374">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>2649</v>
       </c>
@@ -15941,19 +15941,19 @@
         <v>402</v>
       </c>
       <c r="C375" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="D375" t="s">
-        <v>644</v>
+        <v>1988</v>
       </c>
       <c r="E375" t="s">
-        <v>583</v>
+        <v>2522</v>
       </c>
       <c r="I375">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>2649</v>
       </c>
@@ -15961,19 +15961,19 @@
         <v>402</v>
       </c>
       <c r="C376" t="s">
-        <v>1893</v>
+        <v>1896</v>
       </c>
       <c r="D376" t="s">
-        <v>645</v>
+        <v>667</v>
       </c>
       <c r="E376" t="s">
-        <v>646</v>
+        <v>668</v>
       </c>
       <c r="I376">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>2649</v>
       </c>
@@ -15981,19 +15981,19 @@
         <v>402</v>
       </c>
       <c r="C377" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="D377" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="E377" t="s">
-        <v>123</v>
+        <v>658</v>
       </c>
       <c r="I377">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>2649</v>
       </c>
@@ -16001,19 +16001,19 @@
         <v>402</v>
       </c>
       <c r="C378" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="D378" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E378" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I378">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>2649</v>
       </c>
@@ -16021,19 +16021,19 @@
         <v>402</v>
       </c>
       <c r="C379" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="D379" t="s">
-        <v>1986</v>
+        <v>662</v>
       </c>
       <c r="E379" t="s">
-        <v>2520</v>
+        <v>663</v>
       </c>
       <c r="I379">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>2649</v>
       </c>
@@ -16041,19 +16041,19 @@
         <v>402</v>
       </c>
       <c r="C380" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="D380" t="s">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="E380" t="s">
-        <v>596</v>
+        <v>121</v>
       </c>
       <c r="I380">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>2649</v>
       </c>
@@ -16064,16 +16064,16 @@
         <v>1894</v>
       </c>
       <c r="D381" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="E381" t="s">
-        <v>592</v>
+        <v>649</v>
       </c>
       <c r="I381">
         <v>3</v>
       </c>
     </row>
-    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>2649</v>
       </c>
@@ -16081,19 +16081,19 @@
         <v>402</v>
       </c>
       <c r="C382" t="s">
-        <v>1894</v>
+        <v>1890</v>
       </c>
       <c r="D382" t="s">
-        <v>652</v>
+        <v>624</v>
       </c>
       <c r="E382" t="s">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="I382">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>2649</v>
       </c>
@@ -16101,19 +16101,19 @@
         <v>402</v>
       </c>
       <c r="C383" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="D383" t="s">
-        <v>653</v>
+        <v>1992</v>
       </c>
       <c r="E383" t="s">
-        <v>654</v>
+        <v>2525</v>
       </c>
       <c r="I383">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>2649</v>
       </c>
@@ -16121,19 +16121,19 @@
         <v>402</v>
       </c>
       <c r="C384" t="s">
-        <v>1895</v>
+        <v>1890</v>
       </c>
       <c r="D384" t="s">
-        <v>655</v>
+        <v>626</v>
       </c>
       <c r="E384" t="s">
-        <v>656</v>
+        <v>409</v>
       </c>
       <c r="I384">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>2649</v>
       </c>
@@ -16141,19 +16141,19 @@
         <v>402</v>
       </c>
       <c r="C385" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="D385" t="s">
-        <v>1987</v>
+        <v>670</v>
       </c>
       <c r="E385" t="s">
-        <v>2521</v>
+        <v>70</v>
       </c>
       <c r="I385">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>2649</v>
       </c>
@@ -16161,19 +16161,19 @@
         <v>402</v>
       </c>
       <c r="C386" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="D386" t="s">
-        <v>657</v>
+        <v>674</v>
       </c>
       <c r="E386" t="s">
-        <v>658</v>
+        <v>80</v>
       </c>
       <c r="I386">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>2649</v>
       </c>
@@ -16181,19 +16181,19 @@
         <v>402</v>
       </c>
       <c r="C387" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="D387" t="s">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="E387" t="s">
-        <v>600</v>
+        <v>84</v>
       </c>
       <c r="I387">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>2649</v>
       </c>
@@ -16201,19 +16201,19 @@
         <v>402</v>
       </c>
       <c r="C388" t="s">
-        <v>1895</v>
+        <v>1898</v>
       </c>
       <c r="D388" t="s">
-        <v>1988</v>
+        <v>675</v>
       </c>
       <c r="E388" t="s">
-        <v>2522</v>
+        <v>88</v>
       </c>
       <c r="I388">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>2649</v>
       </c>
@@ -16221,19 +16221,19 @@
         <v>402</v>
       </c>
       <c r="C389" t="s">
-        <v>1895</v>
+        <v>1899</v>
       </c>
       <c r="D389" t="s">
-        <v>660</v>
+        <v>676</v>
       </c>
       <c r="E389" t="s">
-        <v>661</v>
+        <v>93</v>
       </c>
       <c r="I389">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>2649</v>
       </c>
@@ -16241,19 +16241,19 @@
         <v>402</v>
       </c>
       <c r="C390" t="s">
-        <v>1895</v>
+        <v>1890</v>
       </c>
       <c r="D390" t="s">
-        <v>662</v>
+        <v>622</v>
       </c>
       <c r="E390" t="s">
-        <v>663</v>
+        <v>13</v>
       </c>
       <c r="I390">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>2649</v>
       </c>
@@ -16261,19 +16261,19 @@
         <v>402</v>
       </c>
       <c r="C391" t="s">
-        <v>1896</v>
+        <v>1891</v>
       </c>
       <c r="D391" t="s">
-        <v>664</v>
+        <v>628</v>
       </c>
       <c r="E391" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="I391">
         <v>4</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>2649</v>
       </c>
@@ -16281,19 +16281,19 @@
         <v>402</v>
       </c>
       <c r="C392" t="s">
-        <v>1896</v>
+        <v>1891</v>
       </c>
       <c r="D392" t="s">
-        <v>665</v>
+        <v>629</v>
       </c>
       <c r="E392" t="s">
-        <v>666</v>
+        <v>27</v>
       </c>
       <c r="I392">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>2649</v>
       </c>
@@ -16301,19 +16301,19 @@
         <v>402</v>
       </c>
       <c r="C393" t="s">
-        <v>1896</v>
+        <v>1892</v>
       </c>
       <c r="D393" t="s">
-        <v>667</v>
+        <v>637</v>
       </c>
       <c r="E393" t="s">
-        <v>668</v>
+        <v>638</v>
       </c>
       <c r="I393">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>2649</v>
       </c>
@@ -16321,19 +16321,19 @@
         <v>402</v>
       </c>
       <c r="C394" t="s">
-        <v>1896</v>
+        <v>1893</v>
       </c>
       <c r="D394" t="s">
-        <v>669</v>
+        <v>643</v>
       </c>
       <c r="E394" t="s">
-        <v>608</v>
+        <v>53</v>
       </c>
       <c r="I394">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>2649</v>
       </c>
@@ -16341,19 +16341,19 @@
         <v>402</v>
       </c>
       <c r="C395" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="D395" t="s">
-        <v>670</v>
+        <v>651</v>
       </c>
       <c r="E395" t="s">
-        <v>70</v>
+        <v>592</v>
       </c>
       <c r="I395">
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>2649</v>
       </c>
@@ -16361,19 +16361,19 @@
         <v>402</v>
       </c>
       <c r="C396" t="s">
-        <v>1896</v>
+        <v>1890</v>
       </c>
       <c r="D396" t="s">
-        <v>1989</v>
+        <v>623</v>
       </c>
       <c r="E396" t="s">
-        <v>2523</v>
+        <v>405</v>
       </c>
       <c r="I396">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>2649</v>
       </c>
@@ -16381,19 +16381,19 @@
         <v>402</v>
       </c>
       <c r="C397" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="D397" t="s">
-        <v>1990</v>
+        <v>660</v>
       </c>
       <c r="E397" t="s">
-        <v>2524</v>
+        <v>661</v>
       </c>
       <c r="I397">
         <v>2</v>
       </c>
     </row>
-    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>2649</v>
       </c>
@@ -16401,19 +16401,19 @@
         <v>402</v>
       </c>
       <c r="C398" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="D398" t="s">
-        <v>671</v>
+        <v>1989</v>
       </c>
       <c r="E398" t="s">
-        <v>672</v>
+        <v>2523</v>
       </c>
       <c r="I398">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>2649</v>
       </c>
@@ -16421,19 +16421,19 @@
         <v>402</v>
       </c>
       <c r="C399" t="s">
-        <v>1897</v>
+        <v>1893</v>
       </c>
       <c r="D399" t="s">
-        <v>1991</v>
+        <v>642</v>
       </c>
       <c r="E399" t="s">
-        <v>283</v>
+        <v>51</v>
       </c>
       <c r="I399">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>2649</v>
       </c>
@@ -16441,19 +16441,19 @@
         <v>402</v>
       </c>
       <c r="C400" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="D400" t="s">
-        <v>673</v>
+        <v>655</v>
       </c>
       <c r="E400" t="s">
-        <v>84</v>
+        <v>656</v>
       </c>
       <c r="I400">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>2649</v>
       </c>
@@ -16461,19 +16461,19 @@
         <v>402</v>
       </c>
       <c r="C401" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="D401" t="s">
-        <v>674</v>
+        <v>1994</v>
       </c>
       <c r="E401" t="s">
-        <v>80</v>
+        <v>389</v>
       </c>
       <c r="I401">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>2649</v>
       </c>
@@ -16481,19 +16481,19 @@
         <v>402</v>
       </c>
       <c r="C402" t="s">
-        <v>1897</v>
+        <v>1893</v>
       </c>
       <c r="D402" t="s">
-        <v>1992</v>
+        <v>641</v>
       </c>
       <c r="E402" t="s">
-        <v>2525</v>
+        <v>49</v>
       </c>
       <c r="I402">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>2649</v>
       </c>
@@ -16501,19 +16501,19 @@
         <v>402</v>
       </c>
       <c r="C403" t="s">
-        <v>1897</v>
+        <v>1891</v>
       </c>
       <c r="D403" t="s">
-        <v>1993</v>
+        <v>631</v>
       </c>
       <c r="E403" t="s">
-        <v>2526</v>
+        <v>112</v>
       </c>
       <c r="I403">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>2649</v>
       </c>
@@ -16521,19 +16521,19 @@
         <v>402</v>
       </c>
       <c r="C404" t="s">
-        <v>1898</v>
+        <v>1890</v>
       </c>
       <c r="D404" t="s">
-        <v>675</v>
+        <v>625</v>
       </c>
       <c r="E404" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="I404">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>2649</v>
       </c>
@@ -16541,19 +16541,19 @@
         <v>402</v>
       </c>
       <c r="C405" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="D405" t="s">
-        <v>1994</v>
+        <v>664</v>
       </c>
       <c r="E405" t="s">
-        <v>389</v>
+        <v>68</v>
       </c>
       <c r="I405">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>2649</v>
       </c>
@@ -16561,19 +16561,19 @@
         <v>402</v>
       </c>
       <c r="C406" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="D406" t="s">
-        <v>676</v>
+        <v>1991</v>
       </c>
       <c r="E406" t="s">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="I406">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>2649</v>
       </c>
@@ -27341,13 +27341,13 @@
         <v>457</v>
       </c>
       <c r="C945" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="D945" t="s">
-        <v>1396</v>
+        <v>1407</v>
       </c>
       <c r="E945" t="s">
-        <v>1281</v>
+        <v>785</v>
       </c>
       <c r="I945">
         <v>4</v>
@@ -27361,13 +27361,13 @@
         <v>457</v>
       </c>
       <c r="C946" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="D946" t="s">
-        <v>1397</v>
+        <v>1404</v>
       </c>
       <c r="E946" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I946">
         <v>4</v>
@@ -27381,13 +27381,13 @@
         <v>457</v>
       </c>
       <c r="C947" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="D947" t="s">
-        <v>1398</v>
+        <v>1415</v>
       </c>
       <c r="E947" t="s">
-        <v>17</v>
+        <v>1309</v>
       </c>
       <c r="I947">
         <v>4</v>
@@ -27401,13 +27401,13 @@
         <v>457</v>
       </c>
       <c r="C948" t="s">
-        <v>1890</v>
+        <v>1895</v>
       </c>
       <c r="D948" t="s">
-        <v>1399</v>
+        <v>2129</v>
       </c>
       <c r="E948" t="s">
-        <v>19</v>
+        <v>2564</v>
       </c>
       <c r="I948">
         <v>4</v>
@@ -27421,13 +27421,13 @@
         <v>457</v>
       </c>
       <c r="C949" t="s">
-        <v>1890</v>
+        <v>1894</v>
       </c>
       <c r="D949" t="s">
-        <v>1400</v>
+        <v>2128</v>
       </c>
       <c r="E949" t="s">
-        <v>21</v>
+        <v>1312</v>
       </c>
       <c r="I949">
         <v>4</v>
@@ -27441,13 +27441,13 @@
         <v>457</v>
       </c>
       <c r="C950" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="D950" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="E950" t="s">
-        <v>1199</v>
+        <v>1213</v>
       </c>
       <c r="I950">
         <v>4</v>
@@ -27461,13 +27461,13 @@
         <v>457</v>
       </c>
       <c r="C951" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="D951" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="E951" t="s">
-        <v>27</v>
+        <v>1212</v>
       </c>
       <c r="I951">
         <v>4</v>
@@ -27481,16 +27481,16 @@
         <v>457</v>
       </c>
       <c r="C952" t="s">
-        <v>1891</v>
+        <v>1899</v>
       </c>
       <c r="D952" t="s">
-        <v>1403</v>
+        <v>2139</v>
       </c>
       <c r="E952" t="s">
-        <v>29</v>
+        <v>1393</v>
       </c>
       <c r="I952">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="953" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27501,13 +27501,13 @@
         <v>457</v>
       </c>
       <c r="C953" t="s">
-        <v>1891</v>
+        <v>1895</v>
       </c>
       <c r="D953" t="s">
-        <v>1404</v>
+        <v>1422</v>
       </c>
       <c r="E953" t="s">
-        <v>31</v>
+        <v>775</v>
       </c>
       <c r="I953">
         <v>4</v>
@@ -27521,13 +27521,13 @@
         <v>457</v>
       </c>
       <c r="C954" t="s">
-        <v>1891</v>
+        <v>1896</v>
       </c>
       <c r="D954" t="s">
-        <v>1405</v>
+        <v>1432</v>
       </c>
       <c r="E954" t="s">
-        <v>1213</v>
+        <v>1433</v>
       </c>
       <c r="I954">
         <v>4</v>
@@ -27541,16 +27541,16 @@
         <v>457</v>
       </c>
       <c r="C955" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D955" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="E955" t="s">
-        <v>1293</v>
+        <v>21</v>
       </c>
       <c r="I955">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="956" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27561,13 +27561,13 @@
         <v>457</v>
       </c>
       <c r="C956" t="s">
-        <v>1892</v>
+        <v>1899</v>
       </c>
       <c r="D956" t="s">
-        <v>1407</v>
+        <v>2138</v>
       </c>
       <c r="E956" t="s">
-        <v>785</v>
+        <v>2570</v>
       </c>
       <c r="I956">
         <v>4</v>
@@ -27581,16 +27581,16 @@
         <v>457</v>
       </c>
       <c r="C957" t="s">
-        <v>1892</v>
+        <v>1899</v>
       </c>
       <c r="D957" t="s">
-        <v>1408</v>
+        <v>1442</v>
       </c>
       <c r="E957" t="s">
-        <v>1212</v>
+        <v>1443</v>
       </c>
       <c r="I957">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="958" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27601,16 +27601,16 @@
         <v>457</v>
       </c>
       <c r="C958" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="D958" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="E958" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="I958">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="959" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27621,16 +27621,16 @@
         <v>457</v>
       </c>
       <c r="C959" t="s">
-        <v>1892</v>
+        <v>1898</v>
       </c>
       <c r="D959" t="s">
-        <v>1410</v>
+        <v>2136</v>
       </c>
       <c r="E959" t="s">
-        <v>1298</v>
+        <v>2568</v>
       </c>
       <c r="I959">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="960" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27641,13 +27641,13 @@
         <v>457</v>
       </c>
       <c r="C960" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="D960" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="E960" t="s">
-        <v>1226</v>
+        <v>1303</v>
       </c>
       <c r="I960">
         <v>4</v>
@@ -27664,10 +27664,10 @@
         <v>1893</v>
       </c>
       <c r="D961" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="E961" t="s">
-        <v>1303</v>
+        <v>1417</v>
       </c>
       <c r="I961">
         <v>4</v>
@@ -27681,13 +27681,13 @@
         <v>457</v>
       </c>
       <c r="C962" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="D962" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E962" t="s">
-        <v>1305</v>
+        <v>1226</v>
       </c>
       <c r="I962">
         <v>4</v>
@@ -27701,16 +27701,16 @@
         <v>457</v>
       </c>
       <c r="C963" t="s">
-        <v>1893</v>
+        <v>1898</v>
       </c>
       <c r="D963" t="s">
-        <v>1414</v>
+        <v>1441</v>
       </c>
       <c r="E963" t="s">
-        <v>1307</v>
+        <v>1386</v>
       </c>
       <c r="I963">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="964" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27721,13 +27721,13 @@
         <v>457</v>
       </c>
       <c r="C964" t="s">
-        <v>1893</v>
+        <v>1890</v>
       </c>
       <c r="D964" t="s">
-        <v>1415</v>
+        <v>1399</v>
       </c>
       <c r="E964" t="s">
-        <v>1309</v>
+        <v>19</v>
       </c>
       <c r="I964">
         <v>4</v>
@@ -27741,13 +27741,13 @@
         <v>457</v>
       </c>
       <c r="C965" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="D965" t="s">
-        <v>1416</v>
+        <v>1409</v>
       </c>
       <c r="E965" t="s">
-        <v>1417</v>
+        <v>1296</v>
       </c>
       <c r="I965">
         <v>4</v>
@@ -27761,13 +27761,13 @@
         <v>457</v>
       </c>
       <c r="C966" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="D966" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="E966" t="s">
-        <v>798</v>
+        <v>1305</v>
       </c>
       <c r="I966">
         <v>4</v>
@@ -27781,13 +27781,13 @@
         <v>457</v>
       </c>
       <c r="C967" t="s">
-        <v>1894</v>
+        <v>1898</v>
       </c>
       <c r="D967" t="s">
-        <v>2128</v>
+        <v>2135</v>
       </c>
       <c r="E967" t="s">
-        <v>1312</v>
+        <v>2567</v>
       </c>
       <c r="I967">
         <v>4</v>
@@ -27801,16 +27801,16 @@
         <v>457</v>
       </c>
       <c r="C968" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="D968" t="s">
-        <v>1419</v>
+        <v>1437</v>
       </c>
       <c r="E968" t="s">
-        <v>1371</v>
+        <v>1012</v>
       </c>
       <c r="I968">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="969" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27821,16 +27821,16 @@
         <v>457</v>
       </c>
       <c r="C969" t="s">
-        <v>1894</v>
+        <v>1899</v>
       </c>
       <c r="D969" t="s">
-        <v>1420</v>
+        <v>1445</v>
       </c>
       <c r="E969" t="s">
-        <v>1316</v>
+        <v>1389</v>
       </c>
       <c r="I969">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="970" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27841,16 +27841,16 @@
         <v>457</v>
       </c>
       <c r="C970" t="s">
-        <v>1894</v>
+        <v>1898</v>
       </c>
       <c r="D970" t="s">
-        <v>1421</v>
+        <v>1440</v>
       </c>
       <c r="E970" t="s">
-        <v>1318</v>
+        <v>1384</v>
       </c>
       <c r="I970">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="971" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27864,13 +27864,13 @@
         <v>1895</v>
       </c>
       <c r="D971" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="E971" t="s">
-        <v>775</v>
+        <v>1323</v>
       </c>
       <c r="I971">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="972" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27901,13 +27901,13 @@
         <v>457</v>
       </c>
       <c r="C973" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="D973" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="E973" t="s">
-        <v>1244</v>
+        <v>1429</v>
       </c>
       <c r="I973">
         <v>4</v>
@@ -27921,16 +27921,16 @@
         <v>457</v>
       </c>
       <c r="C974" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="D974" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="E974" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="I974">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="975" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27941,16 +27941,16 @@
         <v>457</v>
       </c>
       <c r="C975" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="D975" t="s">
-        <v>2129</v>
+        <v>1427</v>
       </c>
       <c r="E975" t="s">
-        <v>2564</v>
+        <v>70</v>
       </c>
       <c r="I975">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="976" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27961,16 +27961,16 @@
         <v>457</v>
       </c>
       <c r="C976" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="D976" t="s">
-        <v>1426</v>
+        <v>1435</v>
       </c>
       <c r="E976" t="s">
-        <v>829</v>
+        <v>80</v>
       </c>
       <c r="I976">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="977" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -27981,16 +27981,16 @@
         <v>457</v>
       </c>
       <c r="C977" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="D977" t="s">
-        <v>1427</v>
+        <v>2133</v>
       </c>
       <c r="E977" t="s">
-        <v>70</v>
+        <v>2565</v>
       </c>
       <c r="I977">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="978" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28001,13 +28001,13 @@
         <v>457</v>
       </c>
       <c r="C978" t="s">
-        <v>1896</v>
+        <v>1890</v>
       </c>
       <c r="D978" t="s">
-        <v>1428</v>
+        <v>1401</v>
       </c>
       <c r="E978" t="s">
-        <v>1429</v>
+        <v>1199</v>
       </c>
       <c r="I978">
         <v>4</v>
@@ -28041,16 +28041,16 @@
         <v>457</v>
       </c>
       <c r="C980" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="D980" t="s">
-        <v>1430</v>
+        <v>2131</v>
       </c>
       <c r="E980" t="s">
-        <v>1431</v>
+        <v>1248</v>
       </c>
       <c r="I980">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="981" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28061,13 +28061,13 @@
         <v>457</v>
       </c>
       <c r="C981" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="D981" t="s">
-        <v>1432</v>
+        <v>1419</v>
       </c>
       <c r="E981" t="s">
-        <v>1433</v>
+        <v>1371</v>
       </c>
       <c r="I981">
         <v>4</v>
@@ -28081,16 +28081,16 @@
         <v>457</v>
       </c>
       <c r="C982" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="D982" t="s">
-        <v>1434</v>
+        <v>1446</v>
       </c>
       <c r="E982" t="s">
-        <v>828</v>
+        <v>1391</v>
       </c>
       <c r="I982">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="983" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28104,10 +28104,10 @@
         <v>1897</v>
       </c>
       <c r="D983" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="E983" t="s">
-        <v>80</v>
+        <v>1439</v>
       </c>
       <c r="I983">
         <v>3</v>
@@ -28141,13 +28141,13 @@
         <v>457</v>
       </c>
       <c r="C985" t="s">
-        <v>1897</v>
+        <v>1890</v>
       </c>
       <c r="D985" t="s">
-        <v>2131</v>
+        <v>1396</v>
       </c>
       <c r="E985" t="s">
-        <v>1248</v>
+        <v>1281</v>
       </c>
       <c r="I985">
         <v>4</v>
@@ -28161,16 +28161,16 @@
         <v>457</v>
       </c>
       <c r="C986" t="s">
-        <v>1897</v>
+        <v>1891</v>
       </c>
       <c r="D986" t="s">
-        <v>1437</v>
+        <v>1402</v>
       </c>
       <c r="E986" t="s">
-        <v>1012</v>
+        <v>27</v>
       </c>
       <c r="I986">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="987" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28181,16 +28181,16 @@
         <v>457</v>
       </c>
       <c r="C987" t="s">
-        <v>1897</v>
+        <v>1890</v>
       </c>
       <c r="D987" t="s">
-        <v>1438</v>
+        <v>1398</v>
       </c>
       <c r="E987" t="s">
-        <v>1439</v>
+        <v>17</v>
       </c>
       <c r="I987">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="988" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28201,16 +28201,16 @@
         <v>457</v>
       </c>
       <c r="C988" t="s">
-        <v>1898</v>
+        <v>1894</v>
       </c>
       <c r="D988" t="s">
-        <v>2132</v>
+        <v>1418</v>
       </c>
       <c r="E988" t="s">
-        <v>91</v>
+        <v>798</v>
       </c>
       <c r="I988">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="989" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28224,10 +28224,10 @@
         <v>1898</v>
       </c>
       <c r="D989" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="E989" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="I989">
         <v>4</v>
@@ -28241,13 +28241,13 @@
         <v>457</v>
       </c>
       <c r="C990" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="D990" t="s">
-        <v>2134</v>
+        <v>2137</v>
       </c>
       <c r="E990" t="s">
-        <v>2566</v>
+        <v>2569</v>
       </c>
       <c r="I990">
         <v>4</v>
@@ -28264,13 +28264,13 @@
         <v>1898</v>
       </c>
       <c r="D991" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
       <c r="E991" t="s">
-        <v>2567</v>
+        <v>91</v>
       </c>
       <c r="I991">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="992" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28281,16 +28281,16 @@
         <v>457</v>
       </c>
       <c r="C992" t="s">
-        <v>1898</v>
+        <v>1893</v>
       </c>
       <c r="D992" t="s">
-        <v>1440</v>
+        <v>1414</v>
       </c>
       <c r="E992" t="s">
-        <v>1384</v>
+        <v>1307</v>
       </c>
       <c r="I992">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="993" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28301,16 +28301,16 @@
         <v>457</v>
       </c>
       <c r="C993" t="s">
-        <v>1898</v>
+        <v>1894</v>
       </c>
       <c r="D993" t="s">
-        <v>2136</v>
+        <v>1420</v>
       </c>
       <c r="E993" t="s">
-        <v>2568</v>
+        <v>1316</v>
       </c>
       <c r="I993">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="994" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28321,16 +28321,16 @@
         <v>457</v>
       </c>
       <c r="C994" t="s">
-        <v>1898</v>
+        <v>1891</v>
       </c>
       <c r="D994" t="s">
-        <v>1441</v>
+        <v>1403</v>
       </c>
       <c r="E994" t="s">
-        <v>1386</v>
+        <v>29</v>
       </c>
       <c r="I994">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="995" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28341,16 +28341,16 @@
         <v>457</v>
       </c>
       <c r="C995" t="s">
-        <v>1899</v>
+        <v>1890</v>
       </c>
       <c r="D995" t="s">
-        <v>1442</v>
+        <v>1397</v>
       </c>
       <c r="E995" t="s">
-        <v>1443</v>
+        <v>15</v>
       </c>
       <c r="I995">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="996" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28361,13 +28361,13 @@
         <v>457</v>
       </c>
       <c r="C996" t="s">
-        <v>1899</v>
+        <v>1895</v>
       </c>
       <c r="D996" t="s">
-        <v>1444</v>
+        <v>1424</v>
       </c>
       <c r="E996" t="s">
-        <v>1339</v>
+        <v>1244</v>
       </c>
       <c r="I996">
         <v>4</v>
@@ -28384,10 +28384,10 @@
         <v>1899</v>
       </c>
       <c r="D997" t="s">
-        <v>2137</v>
+        <v>1444</v>
       </c>
       <c r="E997" t="s">
-        <v>2569</v>
+        <v>1339</v>
       </c>
       <c r="I997">
         <v>4</v>
@@ -28401,16 +28401,16 @@
         <v>457</v>
       </c>
       <c r="C998" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
       <c r="D998" t="s">
-        <v>2138</v>
+        <v>1430</v>
       </c>
       <c r="E998" t="s">
-        <v>2570</v>
+        <v>1431</v>
       </c>
       <c r="I998">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="999" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28421,16 +28421,16 @@
         <v>457</v>
       </c>
       <c r="C999" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
       <c r="D999" t="s">
-        <v>1445</v>
+        <v>1426</v>
       </c>
       <c r="E999" t="s">
-        <v>1389</v>
+        <v>829</v>
       </c>
       <c r="I999">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1000" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28441,16 +28441,16 @@
         <v>457</v>
       </c>
       <c r="C1000" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="D1000" t="s">
-        <v>1446</v>
+        <v>1434</v>
       </c>
       <c r="E1000" t="s">
-        <v>1391</v>
+        <v>828</v>
       </c>
       <c r="I1000">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1001" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -28461,19 +28461,19 @@
         <v>457</v>
       </c>
       <c r="C1001" t="s">
-        <v>1899</v>
+        <v>1892</v>
       </c>
       <c r="D1001" t="s">
-        <v>2139</v>
+        <v>1410</v>
       </c>
       <c r="E1001" t="s">
-        <v>1393</v>
+        <v>1298</v>
       </c>
       <c r="I1001">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>2660</v>
       </c>
@@ -28493,7 +28493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>2660</v>
       </c>
@@ -28513,7 +28513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>2660</v>
       </c>
@@ -28533,7 +28533,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>2660</v>
       </c>
@@ -28553,7 +28553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>2660</v>
       </c>
@@ -28573,7 +28573,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>2660</v>
       </c>
@@ -28593,7 +28593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>2660</v>
       </c>
@@ -28613,7 +28613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>2660</v>
       </c>
@@ -28633,7 +28633,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>2660</v>
       </c>
@@ -28653,7 +28653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>2660</v>
       </c>
@@ -28673,7 +28673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>2660</v>
       </c>
@@ -28693,7 +28693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>2660</v>
       </c>
@@ -28713,7 +28713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>2660</v>
       </c>
@@ -28733,7 +28733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>2660</v>
       </c>
@@ -28753,7 +28753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>2660</v>
       </c>
@@ -28773,7 +28773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>2660</v>
       </c>
@@ -28793,7 +28793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>2660</v>
       </c>
@@ -28813,7 +28813,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>2660</v>
       </c>
@@ -28833,7 +28833,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>2660</v>
       </c>
@@ -28853,7 +28853,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>2660</v>
       </c>
@@ -28873,7 +28873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>2660</v>
       </c>
@@ -28893,7 +28893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>2660</v>
       </c>
@@ -28913,7 +28913,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>2660</v>
       </c>
@@ -28933,7 +28933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>2660</v>
       </c>
@@ -28953,7 +28953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>2660</v>
       </c>
@@ -28973,7 +28973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>2660</v>
       </c>
@@ -28993,7 +28993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>2660</v>
       </c>
@@ -29013,7 +29013,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>2660</v>
       </c>
@@ -29033,7 +29033,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>2660</v>
       </c>
@@ -29053,7 +29053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>2660</v>
       </c>
@@ -29073,7 +29073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>2660</v>
       </c>
@@ -29093,7 +29093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>2660</v>
       </c>
@@ -29113,7 +29113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>2660</v>
       </c>
@@ -29133,7 +29133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>2660</v>
       </c>
@@ -29153,7 +29153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>2660</v>
       </c>
@@ -29173,7 +29173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>2660</v>
       </c>
@@ -29193,7 +29193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>2660</v>
       </c>
@@ -29213,7 +29213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>2660</v>
       </c>
@@ -29233,7 +29233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>2660</v>
       </c>
@@ -29253,7 +29253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>2660</v>
       </c>
@@ -29273,7 +29273,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>2660</v>
       </c>
@@ -29293,7 +29293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>2660</v>
       </c>
@@ -29313,7 +29313,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>2660</v>
       </c>
@@ -29333,7 +29333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>2660</v>
       </c>
@@ -29353,7 +29353,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>2660</v>
       </c>
@@ -29373,7 +29373,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>2660</v>
       </c>
@@ -29393,7 +29393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>2660</v>
       </c>
@@ -29413,7 +29413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>2660</v>
       </c>
@@ -29433,7 +29433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>2660</v>
       </c>
@@ -29453,7 +29453,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>2660</v>
       </c>
@@ -29473,7 +29473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>2660</v>
       </c>
@@ -29493,7 +29493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>2660</v>
       </c>
@@ -29513,7 +29513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>2660</v>
       </c>
@@ -29533,7 +29533,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>2660</v>
       </c>
@@ -29553,7 +29553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>2660</v>
       </c>
@@ -29573,7 +29573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>2660</v>
       </c>
@@ -29593,7 +29593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>2660</v>
       </c>
@@ -48037,9 +48037,12 @@
   <autoFilter ref="A1:J1979" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="IN-202011-AKADEMIC"/>
+        <filter val="EN-202011-AKADEMIC"/>
       </filters>
     </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A354:J407">
+      <sortCondition ref="E1:E1979"/>
+    </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TODOS_PLANES_AKADEMIC.xlsx
+++ b/TODOS_PLANES_AKADEMIC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\OneDrive - UNIVERSIDAD AUTONOMA DE ICA\Escritorio\regulazizacion-aka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0912C3FA-0C51-40EB-AF95-A673A378D90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37EDFCE-F525-471C-A74F-030FA8912417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TODOS_PLANES_AKADEMIC.xlsx
+++ b/TODOS_PLANES_AKADEMIC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\OneDrive - UNIVERSIDAD AUTONOMA DE ICA\Escritorio\regulazizacion-aka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37EDFCE-F525-471C-A74F-030FA8912417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07AEFDBE-C077-4147-98AF-1690F2BEFF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TODOS_PLANES_AKADEMIC.xlsx
+++ b/TODOS_PLANES_AKADEMIC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\OneDrive - UNIVERSIDAD AUTONOMA DE ICA\Escritorio\regulazizacion-aka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07AEFDBE-C077-4147-98AF-1690F2BEFF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2710C9F-8C33-4660-8343-1244B9C8B05C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15513,7 +15513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>2649</v>
       </c>
@@ -15533,7 +15533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>2649</v>
       </c>
@@ -15553,7 +15553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>2649</v>
       </c>
@@ -15573,7 +15573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>2649</v>
       </c>
@@ -15593,7 +15593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>2649</v>
       </c>
@@ -15613,7 +15613,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>2649</v>
       </c>
@@ -15633,7 +15633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>2649</v>
       </c>
@@ -15653,7 +15653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>2649</v>
       </c>
@@ -15673,7 +15673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>2649</v>
       </c>
@@ -15693,7 +15693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>2649</v>
       </c>
@@ -15713,7 +15713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>2649</v>
       </c>
@@ -15733,7 +15733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>2649</v>
       </c>
@@ -15753,7 +15753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>2649</v>
       </c>
@@ -15773,7 +15773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>2649</v>
       </c>
@@ -15793,7 +15793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>2649</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>2649</v>
       </c>
@@ -15833,7 +15833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>2649</v>
       </c>
@@ -15853,7 +15853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>2649</v>
       </c>
@@ -15873,7 +15873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>2649</v>
       </c>
@@ -15893,7 +15893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>2649</v>
       </c>
@@ -15913,7 +15913,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>2649</v>
       </c>
@@ -15933,7 +15933,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>2649</v>
       </c>
@@ -15953,7 +15953,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>2649</v>
       </c>
@@ -15973,7 +15973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>2649</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>2649</v>
       </c>
@@ -16013,7 +16013,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>2649</v>
       </c>
@@ -16033,7 +16033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>2649</v>
       </c>
@@ -16053,7 +16053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>2649</v>
       </c>
@@ -16073,7 +16073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>2649</v>
       </c>
@@ -16093,7 +16093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>2649</v>
       </c>
@@ -16113,7 +16113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>2649</v>
       </c>
@@ -16133,7 +16133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>2649</v>
       </c>
@@ -16153,7 +16153,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>2649</v>
       </c>
@@ -16173,7 +16173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>2649</v>
       </c>
@@ -16193,7 +16193,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>2649</v>
       </c>
@@ -16213,7 +16213,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>2649</v>
       </c>
@@ -16233,7 +16233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>2649</v>
       </c>
@@ -16253,7 +16253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>2649</v>
       </c>
@@ -16273,7 +16273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>2649</v>
       </c>
@@ -16293,7 +16293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>2649</v>
       </c>
@@ -16313,7 +16313,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>2649</v>
       </c>
@@ -16333,7 +16333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>2649</v>
       </c>
@@ -16353,7 +16353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>2649</v>
       </c>
@@ -16373,7 +16373,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>2649</v>
       </c>
@@ -16393,7 +16393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>2649</v>
       </c>
@@ -16413,7 +16413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>2649</v>
       </c>
@@ -16433,7 +16433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>2649</v>
       </c>
@@ -16453,7 +16453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>2649</v>
       </c>
@@ -16473,7 +16473,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>2649</v>
       </c>
@@ -16493,7 +16493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>2649</v>
       </c>
@@ -16513,7 +16513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>2649</v>
       </c>
@@ -16533,7 +16533,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>2649</v>
       </c>
@@ -16553,7 +16553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>2649</v>
       </c>
@@ -16573,7 +16573,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>2649</v>
       </c>
@@ -27573,7 +27573,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="957" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>2659</v>
       </c>
@@ -28253,7 +28253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="991" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>2659</v>
       </c>
@@ -48037,12 +48037,194 @@
   <autoFilter ref="A1:J1979" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="EN-202011-AKADEMIC"/>
+        <filter val="IN-20201-AKADEMIC"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A354:J407">
-      <sortCondition ref="E1:E1979"/>
-    </sortState>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="P06-202011-P061101"/>
+        <filter val="P06-202011-P061102"/>
+        <filter val="P06-202011-P061103"/>
+        <filter val="P06-202011-P061105"/>
+        <filter val="P06-202011-P061106"/>
+        <filter val="P06-202011-P061108"/>
+        <filter val="P06-202011-P061109"/>
+        <filter val="P06-202011-P061110"/>
+        <filter val="P06-202011-P061116"/>
+        <filter val="P06-202011-P061120"/>
+        <filter val="P06-202011-P062104"/>
+        <filter val="P06-202011-P062107"/>
+        <filter val="P06-202011-P062111"/>
+        <filter val="P06-202011-P062112"/>
+        <filter val="P06-202011-P062113"/>
+        <filter val="P06-202011-P062114"/>
+        <filter val="P06-202011-P062115"/>
+        <filter val="P06-202011-P062118"/>
+        <filter val="P06-202011-P062121"/>
+        <filter val="P06-202011-P062125"/>
+        <filter val="P06-202011-P062130"/>
+        <filter val="P06-202011-P062134"/>
+        <filter val="P06-202011-P062137"/>
+        <filter val="P06-202011-P062140"/>
+        <filter val="P06-202011-P062143"/>
+        <filter val="P06-202011-P062144"/>
+        <filter val="P06-202011-P063117"/>
+        <filter val="P06-202011-P063119"/>
+        <filter val="P06-202011-P063122"/>
+        <filter val="P06-202011-P063123"/>
+        <filter val="P06-202011-P063124"/>
+        <filter val="P06-202011-P063126"/>
+        <filter val="P06-202011-P063127"/>
+        <filter val="P06-202011-P063128"/>
+        <filter val="P06-202011-P063129"/>
+        <filter val="P06-202011-P063131"/>
+        <filter val="P06-202011-P063132"/>
+        <filter val="P06-202011-P063133"/>
+        <filter val="P06-202011-P063135"/>
+        <filter val="P06-202011-P063136"/>
+        <filter val="P06-202011-P063138"/>
+        <filter val="P06-202011-P063139"/>
+        <filter val="P06-202011-P063141"/>
+        <filter val="P06-202011-P063142"/>
+        <filter val="P06-202011-P063145"/>
+        <filter val="P06-202011-P063146"/>
+        <filter val="P06-202011-P063147"/>
+        <filter val="P06-202011-P063152"/>
+        <filter val="P06-202011-P063153"/>
+        <filter val="P06-202011-P063154"/>
+        <filter val="P06-202011-P063248"/>
+        <filter val="P06-202011-P063249"/>
+        <filter val="P06-202011-P063250"/>
+        <filter val="P06-202011-P063255"/>
+        <filter val="P06-202011-P063256"/>
+        <filter val="P06-202011-P063257"/>
+        <filter val="P06-202011-P06A2155"/>
+        <filter val="P06-20201-P061101"/>
+        <filter val="P06-20201-P061102"/>
+        <filter val="P06-20201-P061103"/>
+        <filter val="P06-20201-P061105"/>
+        <filter val="P06-20201-P061106"/>
+        <filter val="P06-20201-P061108"/>
+        <filter val="P06-20201-P061109"/>
+        <filter val="P06-20201-P061110"/>
+        <filter val="P06-20201-P061116"/>
+        <filter val="P06-20201-P061120"/>
+        <filter val="P06-20201-P062104"/>
+        <filter val="P06-20201-P062107"/>
+        <filter val="P06-20201-P062111"/>
+        <filter val="P06-20201-P062112"/>
+        <filter val="P06-20201-P062113"/>
+        <filter val="P06-20201-P062114"/>
+        <filter val="P06-20201-P062115"/>
+        <filter val="P06-20201-P062118"/>
+        <filter val="P06-20201-P062121"/>
+        <filter val="P06-20201-P062125"/>
+        <filter val="P06-20201-P062130"/>
+        <filter val="P06-20201-P062134"/>
+        <filter val="P06-20201-P062137"/>
+        <filter val="P06-20201-P062140"/>
+        <filter val="P06-20201-P062143"/>
+        <filter val="P06-20201-P062144"/>
+        <filter val="P06-20201-P062151"/>
+        <filter val="P06-20201-P063117"/>
+        <filter val="P06-20201-P063119"/>
+        <filter val="P06-20201-P063122"/>
+        <filter val="P06-20201-P063123"/>
+        <filter val="P06-20201-P063124"/>
+        <filter val="P06-20201-P063126"/>
+        <filter val="P06-20201-P063127"/>
+        <filter val="P06-20201-P063128"/>
+        <filter val="P06-20201-P063129"/>
+        <filter val="P06-20201-P063131"/>
+        <filter val="P06-20201-P063132"/>
+        <filter val="P06-20201-P063133"/>
+        <filter val="P06-20201-P063135"/>
+        <filter val="P06-20201-P063136"/>
+        <filter val="P06-20201-P063138"/>
+        <filter val="P06-20201-P063139"/>
+        <filter val="P06-20201-P063141"/>
+        <filter val="P06-20201-P063142"/>
+        <filter val="P06-20201-P063145"/>
+        <filter val="P06-20201-P063146"/>
+        <filter val="P06-20201-P063147"/>
+        <filter val="P06-20201-P063152"/>
+        <filter val="P06-20201-P063153"/>
+        <filter val="P06-20201-P063154"/>
+        <filter val="P06-20201-P063248"/>
+        <filter val="P06-20201-P063249"/>
+        <filter val="P06-20201-P063250"/>
+        <filter val="P06-20201-P063255"/>
+        <filter val="P06-20201-P063256"/>
+        <filter val="P06-20201-P063257"/>
+        <filter val="P06-20242-P06A1101"/>
+        <filter val="P06-20242-P06A1102"/>
+        <filter val="P06-20242-P06A1103"/>
+        <filter val="P06-20242-P06A1105"/>
+        <filter val="P06-20242-P06A1106"/>
+        <filter val="P06-20242-P06A1108"/>
+        <filter val="P06-20242-P06A1109"/>
+        <filter val="P06-20242-P06A1110"/>
+        <filter val="P06-20242-P06A1112"/>
+        <filter val="P06-20242-P06A1122"/>
+        <filter val="P06-20242-P06A2104"/>
+        <filter val="P06-20242-P06A2107"/>
+        <filter val="P06-20242-P06A2111"/>
+        <filter val="P06-20242-P06A2113"/>
+        <filter val="P06-20242-P06A2114"/>
+        <filter val="P06-20242-P06A2115"/>
+        <filter val="P06-20242-P06A2117"/>
+        <filter val="P06-20242-P06A2118"/>
+        <filter val="P06-20242-P06A2120"/>
+        <filter val="P06-20242-P06A2123"/>
+        <filter val="P06-20242-P06A2124"/>
+        <filter val="P06-20242-P06A2128"/>
+        <filter val="P06-20242-P06A2130"/>
+        <filter val="P06-20242-P06A2134"/>
+        <filter val="P06-20242-P06A2138"/>
+        <filter val="P06-20242-P06A2141"/>
+        <filter val="P06-20242-P06A2144"/>
+        <filter val="P06-20242-P06A2147"/>
+        <filter val="P06-20242-P06A2148"/>
+        <filter val="P06-20242-P06A2155"/>
+        <filter val="P06-20242-P06A3116"/>
+        <filter val="P06-20242-P06A3119"/>
+        <filter val="P06-20242-P06A3121"/>
+        <filter val="P06-20242-P06A3125"/>
+        <filter val="P06-20242-P06A3126"/>
+        <filter val="P06-20242-P06A3127"/>
+        <filter val="P06-20242-P06A3129"/>
+        <filter val="P06-20242-P06A3131"/>
+        <filter val="P06-20242-P06A3132"/>
+        <filter val="P06-20242-P06A3133"/>
+        <filter val="P06-20242-P06A3135"/>
+        <filter val="P06-20242-P06A3136"/>
+        <filter val="P06-20242-P06A3137"/>
+        <filter val="P06-20242-P06A3139"/>
+        <filter val="P06-20242-P06A3140"/>
+        <filter val="P06-20242-P06A3142"/>
+        <filter val="P06-20242-P06A3143"/>
+        <filter val="P06-20242-P06A3145"/>
+        <filter val="P06-20242-P06A3146"/>
+        <filter val="P06-20242-P06A3149"/>
+        <filter val="P06-20242-P06A3150"/>
+        <filter val="P06-20242-P06A3151"/>
+        <filter val="P06-20242-P06A3157"/>
+        <filter val="P06-20242-P06A3158"/>
+        <filter val="P06-20242-P06A3159"/>
+        <filter val="P06-20242-P06A3252"/>
+        <filter val="P06-20242-P06A3253"/>
+        <filter val="P06-20242-P06A3254"/>
+        <filter val="P06-20242-P06A3260"/>
+        <filter val="P06-20242-P06A3261"/>
+        <filter val="P06-20242-P06A3262"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="DESARROLLO DE TESIS"/>
+        <filter val="PROYECTO DE TESIS"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TODOS_PLANES_AKADEMIC.xlsx
+++ b/TODOS_PLANES_AKADEMIC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\OneDrive - UNIVERSIDAD AUTONOMA DE ICA\Escritorio\regulazizacion-aka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2710C9F-8C33-4660-8343-1244B9C8B05C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B575640-F132-463E-96B0-C7AE98A614CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/TODOS_PLANES_AKADEMIC.xlsx
+++ b/TODOS_PLANES_AKADEMIC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\OneDrive - UNIVERSIDAD AUTONOMA DE ICA\Escritorio\regulazizacion-aka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B575640-F132-463E-96B0-C7AE98A614CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4695DD-9358-4826-867E-99E87C082FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12053,7 +12053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>2645</v>
       </c>
@@ -15353,7 +15353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>2648</v>
       </c>
@@ -16573,7 +16573,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>2649</v>
       </c>
@@ -17633,7 +17633,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>2650</v>
       </c>
@@ -21433,7 +21433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>2653</v>
       </c>
@@ -22533,7 +22533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>2654</v>
       </c>
@@ -24993,7 +24993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="828" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>2656</v>
       </c>
@@ -27233,7 +27233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="940" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>2658</v>
       </c>
@@ -27573,7 +27573,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>2659</v>
       </c>
@@ -28253,7 +28253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>2659</v>
       </c>
@@ -29593,7 +29593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1058" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>2660</v>
       </c>
@@ -30693,7 +30693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
         <v>2661</v>
       </c>
@@ -32033,7 +32033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1180" t="s">
         <v>2662</v>
       </c>
@@ -34253,7 +34253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1291" t="s">
         <v>2664</v>
       </c>
@@ -35833,7 +35833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1370" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1370" t="s">
         <v>2665</v>
       </c>
@@ -38893,7 +38893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1523" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1523" t="s">
         <v>2667</v>
       </c>
@@ -40001,16 +40001,16 @@
         <v>11</v>
       </c>
       <c r="C1578" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="D1578" t="s">
-        <v>923</v>
+        <v>943</v>
       </c>
       <c r="E1578" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="I1578">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1579" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40021,16 +40021,16 @@
         <v>11</v>
       </c>
       <c r="C1579" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="D1579" t="s">
-        <v>924</v>
+        <v>2368</v>
       </c>
       <c r="E1579" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="I1579">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1580" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40041,16 +40041,16 @@
         <v>11</v>
       </c>
       <c r="C1580" t="s">
-        <v>1890</v>
+        <v>1894</v>
       </c>
       <c r="D1580" t="s">
-        <v>925</v>
+        <v>2369</v>
       </c>
       <c r="E1580" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="I1580">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1581" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40061,13 +40061,13 @@
         <v>11</v>
       </c>
       <c r="C1581" t="s">
-        <v>1890</v>
+        <v>1894</v>
       </c>
       <c r="D1581" t="s">
-        <v>926</v>
+        <v>954</v>
       </c>
       <c r="E1581" t="s">
-        <v>19</v>
+        <v>955</v>
       </c>
       <c r="I1581">
         <v>3</v>
@@ -40081,16 +40081,16 @@
         <v>11</v>
       </c>
       <c r="C1582" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="D1582" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="E1582" t="s">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="I1582">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1583" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40101,13 +40101,13 @@
         <v>11</v>
       </c>
       <c r="C1583" t="s">
-        <v>1890</v>
+        <v>1896</v>
       </c>
       <c r="D1583" t="s">
-        <v>928</v>
+        <v>975</v>
       </c>
       <c r="E1583" t="s">
-        <v>929</v>
+        <v>976</v>
       </c>
       <c r="I1583">
         <v>3</v>
@@ -40121,16 +40121,16 @@
         <v>11</v>
       </c>
       <c r="C1584" t="s">
-        <v>1891</v>
+        <v>1898</v>
       </c>
       <c r="D1584" t="s">
-        <v>930</v>
+        <v>2378</v>
       </c>
       <c r="E1584" t="s">
-        <v>25</v>
+        <v>2605</v>
       </c>
       <c r="I1584">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1585" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40141,16 +40141,16 @@
         <v>11</v>
       </c>
       <c r="C1585" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="D1585" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="E1585" t="s">
-        <v>27</v>
+        <v>938</v>
       </c>
       <c r="I1585">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1586" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40161,13 +40161,13 @@
         <v>11</v>
       </c>
       <c r="C1586" t="s">
-        <v>1891</v>
+        <v>1895</v>
       </c>
       <c r="D1586" t="s">
-        <v>932</v>
+        <v>969</v>
       </c>
       <c r="E1586" t="s">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="I1586">
         <v>3</v>
@@ -40181,16 +40181,16 @@
         <v>11</v>
       </c>
       <c r="C1587" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="D1587" t="s">
-        <v>933</v>
+        <v>944</v>
       </c>
       <c r="E1587" t="s">
-        <v>224</v>
+        <v>945</v>
       </c>
       <c r="I1587">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1588" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40201,16 +40201,16 @@
         <v>11</v>
       </c>
       <c r="C1588" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D1588" t="s">
-        <v>2364</v>
+        <v>927</v>
       </c>
       <c r="E1588" t="s">
-        <v>2594</v>
+        <v>21</v>
       </c>
       <c r="I1588">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1589" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40241,16 +40241,16 @@
         <v>11</v>
       </c>
       <c r="C1590" t="s">
-        <v>1892</v>
+        <v>1897</v>
       </c>
       <c r="D1590" t="s">
-        <v>2365</v>
+        <v>2376</v>
       </c>
       <c r="E1590" t="s">
-        <v>2595</v>
+        <v>2614</v>
       </c>
       <c r="I1590">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1591" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40261,13 +40261,13 @@
         <v>11</v>
       </c>
       <c r="C1591" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="D1591" t="s">
-        <v>935</v>
+        <v>950</v>
       </c>
       <c r="E1591" t="s">
-        <v>936</v>
+        <v>951</v>
       </c>
       <c r="I1591">
         <v>3</v>
@@ -40281,13 +40281,13 @@
         <v>11</v>
       </c>
       <c r="C1592" t="s">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="D1592" t="s">
-        <v>937</v>
+        <v>2371</v>
       </c>
       <c r="E1592" t="s">
-        <v>938</v>
+        <v>2599</v>
       </c>
       <c r="I1592">
         <v>3</v>
@@ -40301,16 +40301,16 @@
         <v>11</v>
       </c>
       <c r="C1593" t="s">
-        <v>1892</v>
+        <v>1898</v>
       </c>
       <c r="D1593" t="s">
-        <v>939</v>
+        <v>1000</v>
       </c>
       <c r="E1593" t="s">
-        <v>940</v>
+        <v>1001</v>
       </c>
       <c r="I1593">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1594" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40321,13 +40321,13 @@
         <v>11</v>
       </c>
       <c r="C1594" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="D1594" t="s">
-        <v>941</v>
+        <v>2366</v>
       </c>
       <c r="E1594" t="s">
-        <v>942</v>
+        <v>2613</v>
       </c>
       <c r="I1594">
         <v>3</v>
@@ -40344,10 +40344,10 @@
         <v>1892</v>
       </c>
       <c r="D1595" t="s">
-        <v>943</v>
+        <v>2365</v>
       </c>
       <c r="E1595" t="s">
-        <v>41</v>
+        <v>2595</v>
       </c>
       <c r="I1595">
         <v>3</v>
@@ -40361,13 +40361,13 @@
         <v>11</v>
       </c>
       <c r="C1596" t="s">
-        <v>1892</v>
+        <v>1897</v>
       </c>
       <c r="D1596" t="s">
-        <v>944</v>
+        <v>982</v>
       </c>
       <c r="E1596" t="s">
-        <v>945</v>
+        <v>983</v>
       </c>
       <c r="I1596">
         <v>3</v>
@@ -40381,13 +40381,13 @@
         <v>11</v>
       </c>
       <c r="C1597" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="D1597" t="s">
-        <v>2366</v>
+        <v>935</v>
       </c>
       <c r="E1597" t="s">
-        <v>2613</v>
+        <v>936</v>
       </c>
       <c r="I1597">
         <v>3</v>
@@ -40404,10 +40404,10 @@
         <v>1893</v>
       </c>
       <c r="D1598" t="s">
-        <v>2367</v>
+        <v>946</v>
       </c>
       <c r="E1598" t="s">
-        <v>2597</v>
+        <v>947</v>
       </c>
       <c r="I1598">
         <v>3</v>
@@ -40421,16 +40421,16 @@
         <v>11</v>
       </c>
       <c r="C1599" t="s">
-        <v>1893</v>
+        <v>1898</v>
       </c>
       <c r="D1599" t="s">
-        <v>946</v>
+        <v>2380</v>
       </c>
       <c r="E1599" t="s">
-        <v>947</v>
+        <v>2606</v>
       </c>
       <c r="I1599">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1600" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40441,13 +40441,13 @@
         <v>11</v>
       </c>
       <c r="C1600" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="D1600" t="s">
-        <v>948</v>
+        <v>965</v>
       </c>
       <c r="E1600" t="s">
-        <v>949</v>
+        <v>966</v>
       </c>
       <c r="I1600">
         <v>3</v>
@@ -40461,16 +40461,16 @@
         <v>11</v>
       </c>
       <c r="C1601" t="s">
-        <v>1893</v>
+        <v>1899</v>
       </c>
       <c r="D1601" t="s">
-        <v>950</v>
+        <v>1015</v>
       </c>
       <c r="E1601" t="s">
-        <v>951</v>
+        <v>1016</v>
       </c>
       <c r="I1601">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1602" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40481,13 +40481,13 @@
         <v>11</v>
       </c>
       <c r="C1602" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="D1602" t="s">
-        <v>2368</v>
+        <v>960</v>
       </c>
       <c r="E1602" t="s">
-        <v>115</v>
+        <v>961</v>
       </c>
       <c r="I1602">
         <v>3</v>
@@ -40501,13 +40501,13 @@
         <v>11</v>
       </c>
       <c r="C1603" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="D1603" t="s">
-        <v>952</v>
+        <v>967</v>
       </c>
       <c r="E1603" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
       <c r="I1603">
         <v>3</v>
@@ -40521,13 +40521,13 @@
         <v>11</v>
       </c>
       <c r="C1604" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="D1604" t="s">
-        <v>954</v>
+        <v>964</v>
       </c>
       <c r="E1604" t="s">
-        <v>955</v>
+        <v>788</v>
       </c>
       <c r="I1604">
         <v>3</v>
@@ -40541,13 +40541,13 @@
         <v>11</v>
       </c>
       <c r="C1605" t="s">
-        <v>1894</v>
+        <v>1898</v>
       </c>
       <c r="D1605" t="s">
-        <v>956</v>
+        <v>2379</v>
       </c>
       <c r="E1605" t="s">
-        <v>957</v>
+        <v>1185</v>
       </c>
       <c r="I1605">
         <v>3</v>
@@ -40561,13 +40561,13 @@
         <v>11</v>
       </c>
       <c r="C1606" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="D1606" t="s">
-        <v>2369</v>
+        <v>984</v>
       </c>
       <c r="E1606" t="s">
-        <v>123</v>
+        <v>985</v>
       </c>
       <c r="I1606">
         <v>3</v>
@@ -40581,16 +40581,16 @@
         <v>11</v>
       </c>
       <c r="C1607" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="D1607" t="s">
-        <v>958</v>
+        <v>988</v>
       </c>
       <c r="E1607" t="s">
-        <v>959</v>
+        <v>989</v>
       </c>
       <c r="I1607">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1608" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40604,10 +40604,10 @@
         <v>1894</v>
       </c>
       <c r="D1608" t="s">
-        <v>960</v>
+        <v>2370</v>
       </c>
       <c r="E1608" t="s">
-        <v>961</v>
+        <v>2598</v>
       </c>
       <c r="I1608">
         <v>3</v>
@@ -40621,13 +40621,13 @@
         <v>11</v>
       </c>
       <c r="C1609" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="D1609" t="s">
-        <v>962</v>
+        <v>952</v>
       </c>
       <c r="E1609" t="s">
-        <v>963</v>
+        <v>953</v>
       </c>
       <c r="I1609">
         <v>3</v>
@@ -40641,13 +40641,13 @@
         <v>11</v>
       </c>
       <c r="C1610" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="D1610" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="E1610" t="s">
-        <v>2598</v>
+        <v>2600</v>
       </c>
       <c r="I1610">
         <v>3</v>
@@ -40661,13 +40661,13 @@
         <v>11</v>
       </c>
       <c r="C1611" t="s">
-        <v>1895</v>
+        <v>1899</v>
       </c>
       <c r="D1611" t="s">
-        <v>964</v>
+        <v>1003</v>
       </c>
       <c r="E1611" t="s">
-        <v>788</v>
+        <v>1004</v>
       </c>
       <c r="I1611">
         <v>3</v>
@@ -40681,13 +40681,13 @@
         <v>11</v>
       </c>
       <c r="C1612" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="D1612" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
       <c r="E1612" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
       <c r="I1612">
         <v>3</v>
@@ -40701,13 +40701,13 @@
         <v>11</v>
       </c>
       <c r="C1613" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="D1613" t="s">
-        <v>967</v>
+        <v>956</v>
       </c>
       <c r="E1613" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="I1613">
         <v>3</v>
@@ -40721,16 +40721,16 @@
         <v>11</v>
       </c>
       <c r="C1614" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="D1614" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="E1614" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="I1614">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1615" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40741,13 +40741,13 @@
         <v>11</v>
       </c>
       <c r="C1615" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="D1615" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
       <c r="E1615" t="s">
-        <v>2599</v>
+        <v>1137</v>
       </c>
       <c r="I1615">
         <v>3</v>
@@ -40761,13 +40761,13 @@
         <v>11</v>
       </c>
       <c r="C1616" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="D1616" t="s">
-        <v>2372</v>
+        <v>986</v>
       </c>
       <c r="E1616" t="s">
-        <v>2600</v>
+        <v>987</v>
       </c>
       <c r="I1616">
         <v>3</v>
@@ -40781,13 +40781,13 @@
         <v>11</v>
       </c>
       <c r="C1617" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="D1617" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="E1617" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="I1617">
         <v>3</v>
@@ -40801,13 +40801,13 @@
         <v>11</v>
       </c>
       <c r="C1618" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="D1618" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="E1618" t="s">
-        <v>70</v>
+        <v>972</v>
       </c>
       <c r="I1618">
         <v>3</v>
@@ -40821,16 +40821,16 @@
         <v>11</v>
       </c>
       <c r="C1619" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="D1619" t="s">
-        <v>974</v>
+        <v>962</v>
       </c>
       <c r="E1619" t="s">
-        <v>68</v>
+        <v>963</v>
       </c>
       <c r="I1619">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1620" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40841,16 +40841,16 @@
         <v>11</v>
       </c>
       <c r="C1620" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="D1620" t="s">
-        <v>975</v>
+        <v>998</v>
       </c>
       <c r="E1620" t="s">
-        <v>976</v>
+        <v>999</v>
       </c>
       <c r="I1620">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1621" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40861,16 +40861,16 @@
         <v>11</v>
       </c>
       <c r="C1621" t="s">
-        <v>1896</v>
+        <v>1891</v>
       </c>
       <c r="D1621" t="s">
-        <v>977</v>
+        <v>2364</v>
       </c>
       <c r="E1621" t="s">
-        <v>978</v>
+        <v>2594</v>
       </c>
       <c r="I1621">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1622" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40881,13 +40881,13 @@
         <v>11</v>
       </c>
       <c r="C1622" t="s">
-        <v>1896</v>
+        <v>1892</v>
       </c>
       <c r="D1622" t="s">
-        <v>2373</v>
+        <v>939</v>
       </c>
       <c r="E1622" t="s">
-        <v>1137</v>
+        <v>940</v>
       </c>
       <c r="I1622">
         <v>3</v>
@@ -40901,16 +40901,16 @@
         <v>11</v>
       </c>
       <c r="C1623" t="s">
-        <v>1896</v>
+        <v>1890</v>
       </c>
       <c r="D1623" t="s">
-        <v>979</v>
+        <v>926</v>
       </c>
       <c r="E1623" t="s">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="I1623">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1624" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40924,13 +40924,13 @@
         <v>1897</v>
       </c>
       <c r="D1624" t="s">
-        <v>981</v>
+        <v>990</v>
       </c>
       <c r="E1624" t="s">
-        <v>80</v>
+        <v>991</v>
       </c>
       <c r="I1624">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1625" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40941,16 +40941,16 @@
         <v>11</v>
       </c>
       <c r="C1625" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="D1625" t="s">
-        <v>2374</v>
+        <v>1011</v>
       </c>
       <c r="E1625" t="s">
-        <v>283</v>
+        <v>1012</v>
       </c>
       <c r="I1625">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1626" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -40961,13 +40961,13 @@
         <v>11</v>
       </c>
       <c r="C1626" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="D1626" t="s">
-        <v>982</v>
+        <v>994</v>
       </c>
       <c r="E1626" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="I1626">
         <v>3</v>
@@ -40981,13 +40981,13 @@
         <v>11</v>
       </c>
       <c r="C1627" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="D1627" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="E1627" t="s">
-        <v>985</v>
+        <v>70</v>
       </c>
       <c r="I1627">
         <v>3</v>
@@ -41004,10 +41004,10 @@
         <v>1897</v>
       </c>
       <c r="D1628" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="E1628" t="s">
-        <v>987</v>
+        <v>80</v>
       </c>
       <c r="I1628">
         <v>3</v>
@@ -41021,13 +41021,13 @@
         <v>11</v>
       </c>
       <c r="C1629" t="s">
-        <v>1897</v>
+        <v>1890</v>
       </c>
       <c r="D1629" t="s">
-        <v>2375</v>
+        <v>928</v>
       </c>
       <c r="E1629" t="s">
-        <v>2603</v>
+        <v>929</v>
       </c>
       <c r="I1629">
         <v>3</v>
@@ -41041,16 +41041,16 @@
         <v>11</v>
       </c>
       <c r="C1630" t="s">
-        <v>1897</v>
+        <v>1890</v>
       </c>
       <c r="D1630" t="s">
-        <v>2376</v>
+        <v>923</v>
       </c>
       <c r="E1630" t="s">
-        <v>2614</v>
+        <v>13</v>
       </c>
       <c r="I1630">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1631" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41061,16 +41061,16 @@
         <v>11</v>
       </c>
       <c r="C1631" t="s">
-        <v>1897</v>
+        <v>1891</v>
       </c>
       <c r="D1631" t="s">
-        <v>988</v>
+        <v>930</v>
       </c>
       <c r="E1631" t="s">
-        <v>989</v>
+        <v>25</v>
       </c>
       <c r="I1631">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1632" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41081,16 +41081,16 @@
         <v>11</v>
       </c>
       <c r="C1632" t="s">
-        <v>1897</v>
+        <v>1893</v>
       </c>
       <c r="D1632" t="s">
-        <v>990</v>
+        <v>2367</v>
       </c>
       <c r="E1632" t="s">
-        <v>991</v>
+        <v>2597</v>
       </c>
       <c r="I1632">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1633" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41101,16 +41101,16 @@
         <v>11</v>
       </c>
       <c r="C1633" t="s">
-        <v>1898</v>
+        <v>1891</v>
       </c>
       <c r="D1633" t="s">
-        <v>2377</v>
+        <v>931</v>
       </c>
       <c r="E1633" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="I1633">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1634" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41121,16 +41121,16 @@
         <v>11</v>
       </c>
       <c r="C1634" t="s">
-        <v>1898</v>
+        <v>1890</v>
       </c>
       <c r="D1634" t="s">
-        <v>992</v>
+        <v>925</v>
       </c>
       <c r="E1634" t="s">
-        <v>993</v>
+        <v>17</v>
       </c>
       <c r="I1634">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1635" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41144,13 +41144,13 @@
         <v>1898</v>
       </c>
       <c r="D1635" t="s">
-        <v>994</v>
+        <v>2377</v>
       </c>
       <c r="E1635" t="s">
-        <v>995</v>
+        <v>91</v>
       </c>
       <c r="I1635">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1636" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41161,13 +41161,13 @@
         <v>11</v>
       </c>
       <c r="C1636" t="s">
-        <v>1898</v>
+        <v>1893</v>
       </c>
       <c r="D1636" t="s">
-        <v>2378</v>
+        <v>948</v>
       </c>
       <c r="E1636" t="s">
-        <v>2605</v>
+        <v>949</v>
       </c>
       <c r="I1636">
         <v>3</v>
@@ -41181,13 +41181,13 @@
         <v>11</v>
       </c>
       <c r="C1637" t="s">
-        <v>1898</v>
+        <v>1891</v>
       </c>
       <c r="D1637" t="s">
-        <v>2379</v>
+        <v>932</v>
       </c>
       <c r="E1637" t="s">
-        <v>1185</v>
+        <v>29</v>
       </c>
       <c r="I1637">
         <v>3</v>
@@ -41201,16 +41201,16 @@
         <v>11</v>
       </c>
       <c r="C1638" t="s">
-        <v>1898</v>
+        <v>1890</v>
       </c>
       <c r="D1638" t="s">
-        <v>2380</v>
+        <v>924</v>
       </c>
       <c r="E1638" t="s">
-        <v>2606</v>
+        <v>15</v>
       </c>
       <c r="I1638">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1639" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41241,16 +41241,16 @@
         <v>11</v>
       </c>
       <c r="C1640" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="D1640" t="s">
-        <v>998</v>
+        <v>1009</v>
       </c>
       <c r="E1640" t="s">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="I1640">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1641" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41261,16 +41261,16 @@
         <v>11</v>
       </c>
       <c r="C1641" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="D1641" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="E1641" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="I1641">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1642" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41284,13 +41284,13 @@
         <v>1899</v>
       </c>
       <c r="D1642" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="E1642" t="s">
-        <v>161</v>
+        <v>1006</v>
       </c>
       <c r="I1642">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1643" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41304,13 +41304,13 @@
         <v>1899</v>
       </c>
       <c r="D1643" t="s">
-        <v>1003</v>
+        <v>1013</v>
       </c>
       <c r="E1643" t="s">
-        <v>1004</v>
+        <v>1014</v>
       </c>
       <c r="I1643">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1644" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41321,16 +41321,16 @@
         <v>11</v>
       </c>
       <c r="C1644" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
       <c r="D1644" t="s">
-        <v>1005</v>
+        <v>974</v>
       </c>
       <c r="E1644" t="s">
-        <v>1006</v>
+        <v>68</v>
       </c>
       <c r="I1644">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1645" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41341,16 +41341,16 @@
         <v>11</v>
       </c>
       <c r="C1645" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="D1645" t="s">
-        <v>1007</v>
+        <v>2374</v>
       </c>
       <c r="E1645" t="s">
-        <v>1008</v>
+        <v>283</v>
       </c>
       <c r="I1645">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1646" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41361,13 +41361,13 @@
         <v>11</v>
       </c>
       <c r="C1646" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="D1646" t="s">
-        <v>1009</v>
+        <v>992</v>
       </c>
       <c r="E1646" t="s">
-        <v>1010</v>
+        <v>993</v>
       </c>
       <c r="I1646">
         <v>3</v>
@@ -41381,19 +41381,19 @@
         <v>11</v>
       </c>
       <c r="C1647" t="s">
-        <v>1899</v>
+        <v>1892</v>
       </c>
       <c r="D1647" t="s">
-        <v>1011</v>
+        <v>941</v>
       </c>
       <c r="E1647" t="s">
-        <v>1012</v>
+        <v>942</v>
       </c>
       <c r="I1647">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1648" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1648" t="s">
         <v>2669</v>
       </c>
@@ -41404,13 +41404,13 @@
         <v>1899</v>
       </c>
       <c r="D1648" t="s">
-        <v>1013</v>
+        <v>1002</v>
       </c>
       <c r="E1648" t="s">
-        <v>1014</v>
+        <v>161</v>
       </c>
       <c r="I1648">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1649" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -41421,16 +41421,16 @@
         <v>11</v>
       </c>
       <c r="C1649" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="D1649" t="s">
-        <v>1015</v>
+        <v>2375</v>
       </c>
       <c r="E1649" t="s">
-        <v>1016</v>
+        <v>2603</v>
       </c>
       <c r="I1649">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1650" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -42493,7 +42493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1703" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1703" t="s">
         <v>2670</v>
       </c>
@@ -44773,7 +44773,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1817" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1817" t="s">
         <v>2672</v>
       </c>
@@ -46353,7 +46353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1896" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1896" t="s">
         <v>2673</v>
       </c>
@@ -47893,7 +47893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1973" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1973" t="s">
         <v>2674</v>
       </c>
@@ -48035,196 +48035,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J1979" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
+    <filterColumn colId="4">
       <filters>
-        <filter val="IN-20201-AKADEMIC"/>
+        <filter val="TRABAJO DE INVESTIGACIÓN"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="P06-202011-P061101"/>
-        <filter val="P06-202011-P061102"/>
-        <filter val="P06-202011-P061103"/>
-        <filter val="P06-202011-P061105"/>
-        <filter val="P06-202011-P061106"/>
-        <filter val="P06-202011-P061108"/>
-        <filter val="P06-202011-P061109"/>
-        <filter val="P06-202011-P061110"/>
-        <filter val="P06-202011-P061116"/>
-        <filter val="P06-202011-P061120"/>
-        <filter val="P06-202011-P062104"/>
-        <filter val="P06-202011-P062107"/>
-        <filter val="P06-202011-P062111"/>
-        <filter val="P06-202011-P062112"/>
-        <filter val="P06-202011-P062113"/>
-        <filter val="P06-202011-P062114"/>
-        <filter val="P06-202011-P062115"/>
-        <filter val="P06-202011-P062118"/>
-        <filter val="P06-202011-P062121"/>
-        <filter val="P06-202011-P062125"/>
-        <filter val="P06-202011-P062130"/>
-        <filter val="P06-202011-P062134"/>
-        <filter val="P06-202011-P062137"/>
-        <filter val="P06-202011-P062140"/>
-        <filter val="P06-202011-P062143"/>
-        <filter val="P06-202011-P062144"/>
-        <filter val="P06-202011-P063117"/>
-        <filter val="P06-202011-P063119"/>
-        <filter val="P06-202011-P063122"/>
-        <filter val="P06-202011-P063123"/>
-        <filter val="P06-202011-P063124"/>
-        <filter val="P06-202011-P063126"/>
-        <filter val="P06-202011-P063127"/>
-        <filter val="P06-202011-P063128"/>
-        <filter val="P06-202011-P063129"/>
-        <filter val="P06-202011-P063131"/>
-        <filter val="P06-202011-P063132"/>
-        <filter val="P06-202011-P063133"/>
-        <filter val="P06-202011-P063135"/>
-        <filter val="P06-202011-P063136"/>
-        <filter val="P06-202011-P063138"/>
-        <filter val="P06-202011-P063139"/>
-        <filter val="P06-202011-P063141"/>
-        <filter val="P06-202011-P063142"/>
-        <filter val="P06-202011-P063145"/>
-        <filter val="P06-202011-P063146"/>
-        <filter val="P06-202011-P063147"/>
-        <filter val="P06-202011-P063152"/>
-        <filter val="P06-202011-P063153"/>
-        <filter val="P06-202011-P063154"/>
-        <filter val="P06-202011-P063248"/>
-        <filter val="P06-202011-P063249"/>
-        <filter val="P06-202011-P063250"/>
-        <filter val="P06-202011-P063255"/>
-        <filter val="P06-202011-P063256"/>
-        <filter val="P06-202011-P063257"/>
-        <filter val="P06-202011-P06A2155"/>
-        <filter val="P06-20201-P061101"/>
-        <filter val="P06-20201-P061102"/>
-        <filter val="P06-20201-P061103"/>
-        <filter val="P06-20201-P061105"/>
-        <filter val="P06-20201-P061106"/>
-        <filter val="P06-20201-P061108"/>
-        <filter val="P06-20201-P061109"/>
-        <filter val="P06-20201-P061110"/>
-        <filter val="P06-20201-P061116"/>
-        <filter val="P06-20201-P061120"/>
-        <filter val="P06-20201-P062104"/>
-        <filter val="P06-20201-P062107"/>
-        <filter val="P06-20201-P062111"/>
-        <filter val="P06-20201-P062112"/>
-        <filter val="P06-20201-P062113"/>
-        <filter val="P06-20201-P062114"/>
-        <filter val="P06-20201-P062115"/>
-        <filter val="P06-20201-P062118"/>
-        <filter val="P06-20201-P062121"/>
-        <filter val="P06-20201-P062125"/>
-        <filter val="P06-20201-P062130"/>
-        <filter val="P06-20201-P062134"/>
-        <filter val="P06-20201-P062137"/>
-        <filter val="P06-20201-P062140"/>
-        <filter val="P06-20201-P062143"/>
-        <filter val="P06-20201-P062144"/>
-        <filter val="P06-20201-P062151"/>
-        <filter val="P06-20201-P063117"/>
-        <filter val="P06-20201-P063119"/>
-        <filter val="P06-20201-P063122"/>
-        <filter val="P06-20201-P063123"/>
-        <filter val="P06-20201-P063124"/>
-        <filter val="P06-20201-P063126"/>
-        <filter val="P06-20201-P063127"/>
-        <filter val="P06-20201-P063128"/>
-        <filter val="P06-20201-P063129"/>
-        <filter val="P06-20201-P063131"/>
-        <filter val="P06-20201-P063132"/>
-        <filter val="P06-20201-P063133"/>
-        <filter val="P06-20201-P063135"/>
-        <filter val="P06-20201-P063136"/>
-        <filter val="P06-20201-P063138"/>
-        <filter val="P06-20201-P063139"/>
-        <filter val="P06-20201-P063141"/>
-        <filter val="P06-20201-P063142"/>
-        <filter val="P06-20201-P063145"/>
-        <filter val="P06-20201-P063146"/>
-        <filter val="P06-20201-P063147"/>
-        <filter val="P06-20201-P063152"/>
-        <filter val="P06-20201-P063153"/>
-        <filter val="P06-20201-P063154"/>
-        <filter val="P06-20201-P063248"/>
-        <filter val="P06-20201-P063249"/>
-        <filter val="P06-20201-P063250"/>
-        <filter val="P06-20201-P063255"/>
-        <filter val="P06-20201-P063256"/>
-        <filter val="P06-20201-P063257"/>
-        <filter val="P06-20242-P06A1101"/>
-        <filter val="P06-20242-P06A1102"/>
-        <filter val="P06-20242-P06A1103"/>
-        <filter val="P06-20242-P06A1105"/>
-        <filter val="P06-20242-P06A1106"/>
-        <filter val="P06-20242-P06A1108"/>
-        <filter val="P06-20242-P06A1109"/>
-        <filter val="P06-20242-P06A1110"/>
-        <filter val="P06-20242-P06A1112"/>
-        <filter val="P06-20242-P06A1122"/>
-        <filter val="P06-20242-P06A2104"/>
-        <filter val="P06-20242-P06A2107"/>
-        <filter val="P06-20242-P06A2111"/>
-        <filter val="P06-20242-P06A2113"/>
-        <filter val="P06-20242-P06A2114"/>
-        <filter val="P06-20242-P06A2115"/>
-        <filter val="P06-20242-P06A2117"/>
-        <filter val="P06-20242-P06A2118"/>
-        <filter val="P06-20242-P06A2120"/>
-        <filter val="P06-20242-P06A2123"/>
-        <filter val="P06-20242-P06A2124"/>
-        <filter val="P06-20242-P06A2128"/>
-        <filter val="P06-20242-P06A2130"/>
-        <filter val="P06-20242-P06A2134"/>
-        <filter val="P06-20242-P06A2138"/>
-        <filter val="P06-20242-P06A2141"/>
-        <filter val="P06-20242-P06A2144"/>
-        <filter val="P06-20242-P06A2147"/>
-        <filter val="P06-20242-P06A2148"/>
-        <filter val="P06-20242-P06A2155"/>
-        <filter val="P06-20242-P06A3116"/>
-        <filter val="P06-20242-P06A3119"/>
-        <filter val="P06-20242-P06A3121"/>
-        <filter val="P06-20242-P06A3125"/>
-        <filter val="P06-20242-P06A3126"/>
-        <filter val="P06-20242-P06A3127"/>
-        <filter val="P06-20242-P06A3129"/>
-        <filter val="P06-20242-P06A3131"/>
-        <filter val="P06-20242-P06A3132"/>
-        <filter val="P06-20242-P06A3133"/>
-        <filter val="P06-20242-P06A3135"/>
-        <filter val="P06-20242-P06A3136"/>
-        <filter val="P06-20242-P06A3137"/>
-        <filter val="P06-20242-P06A3139"/>
-        <filter val="P06-20242-P06A3140"/>
-        <filter val="P06-20242-P06A3142"/>
-        <filter val="P06-20242-P06A3143"/>
-        <filter val="P06-20242-P06A3145"/>
-        <filter val="P06-20242-P06A3146"/>
-        <filter val="P06-20242-P06A3149"/>
-        <filter val="P06-20242-P06A3150"/>
-        <filter val="P06-20242-P06A3151"/>
-        <filter val="P06-20242-P06A3157"/>
-        <filter val="P06-20242-P06A3158"/>
-        <filter val="P06-20242-P06A3159"/>
-        <filter val="P06-20242-P06A3252"/>
-        <filter val="P06-20242-P06A3253"/>
-        <filter val="P06-20242-P06A3254"/>
-        <filter val="P06-20242-P06A3260"/>
-        <filter val="P06-20242-P06A3261"/>
-        <filter val="P06-20242-P06A3262"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="DESARROLLO DE TESIS"/>
-        <filter val="PROYECTO DE TESIS"/>
-      </filters>
-    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1578:J1649">
+      <sortCondition ref="E1:E1979"/>
+    </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
